--- a/ids541_specific/class_schedule_541_xlsx.xlsx
+++ b/ids541_specific/class_schedule_541_xlsx.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids541_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050B5288-67BD-1D4A-A9EB-9E287AAB66B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24EC3548-B9B7-FB41-9909-5A220E8D9436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17520" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
   </bookViews>
@@ -271,32 +271,32 @@
     <t>- `Mapping &lt;exercises/exercise_mapping.html&gt;`_</t>
   </si>
   <si>
+    <t>- `Mapping &lt;../notebooks/gis/25_gis_mapping.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Census &lt;exercises/exercise_census.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- Community Detection
+- Shortest Path</t>
+  </si>
+  <si>
+    <t>- More Dask</t>
+  </si>
+  <si>
+    <t>- `Dask &lt;exercises/exercise_dask.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Dask ARCOS &lt;exercises/exercise_dask_arcos.html&gt;`_</t>
+  </si>
+  <si>
+    <t>**SNOW**</t>
+  </si>
+  <si>
     <t xml:space="preserve">- `What is GIS? &lt;../notebooks/gis/10_gis_what_is_gis.html&gt;`_
-- `Installing Geopandas &lt;../notebooks/gis/15_gis_setup_geopanda.html&gt;`_
+- `Installing Geopandas &lt;../notebooks/gis/15_gis_setup_geopandas.html&gt;`_
 - `Intro to Geopandas &lt;../notebooks/gis/20_gis_geopandas.html&gt;`_
 </t>
-  </si>
-  <si>
-    <t>- `Mapping &lt;../notebooks/gis/25_gis_mapping.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `Census &lt;exercises/exercise_census.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- Community Detection
-- Shortest Path</t>
-  </si>
-  <si>
-    <t>- More Dask</t>
-  </si>
-  <si>
-    <t>- `Dask &lt;exercises/exercise_dask.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `Dask ARCOS &lt;exercises/exercise_dask_arcos.html&gt;`_</t>
-  </si>
-  <si>
-    <t>**SNOW**</t>
   </si>
 </sst>
 </file>
@@ -763,7 +763,7 @@
         <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.2">
@@ -777,7 +777,7 @@
         <v>7</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -785,10 +785,10 @@
         <v>32</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="118" customHeight="1" x14ac:dyDescent="0.2">
@@ -799,10 +799,10 @@
         <v>21</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -813,7 +813,7 @@
         <v>21</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>70</v>
@@ -1024,7 +1024,7 @@
         <v>10</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">

--- a/ids541_specific/class_schedule_541_xlsx.xlsx
+++ b/ids541_specific/class_schedule_541_xlsx.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids541_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24EC3548-B9B7-FB41-9909-5A220E8D9436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04336209-CB4E-B249-B640-5CEB49E5EC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17520" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="78">
   <si>
     <t>Topic</t>
   </si>
@@ -109,12 +109,6 @@
   </si>
   <si>
     <t>-GIS: Vector Data</t>
-  </si>
-  <si>
-    <t>- Solving Problems with Data</t>
-  </si>
-  <si>
-    <t>- `Solving Problems with Data &lt;https://ds4humans.com/10_introduction/10_solving_problems_with_data.html&gt;`_</t>
   </si>
   <si>
     <t>- Géron, Chpt 1: The Machine Learning Landscape (stop before "Batch and Online Learning," then read the "Testing and Validating" section)
@@ -297,6 +291,9 @@
 - `Installing Geopandas &lt;../notebooks/gis/15_gis_setup_geopandas.html&gt;`_
 - `Intro to Geopandas &lt;../notebooks/gis/20_gis_geopandas.html&gt;`_
 </t>
+  </si>
+  <si>
+    <t>**SNOW AGAIN**</t>
   </si>
 </sst>
 </file>
@@ -713,24 +710,24 @@
     </row>
     <row r="2" spans="1:4" ht="204" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="204" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>9</v>
@@ -738,15 +735,15 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>3</v>
@@ -760,15 +757,15 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>6</v>
@@ -777,236 +774,233 @@
         <v>7</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>76</v>
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="118" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" s="8" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="D9" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="7"/>
-    </row>
-    <row r="13" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" s="8"/>
-    </row>
-    <row r="14" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="D13" s="7"/>
+    </row>
+    <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D14" s="8"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="C15" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="8"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+      <c r="C16" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>65</v>
+        <v>20</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="106" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>14</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="136" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>63</v>
+      <c r="D24" s="7" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="134" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="103" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>23</v>
+        <v>53</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
@@ -1018,18 +1012,18 @@
     </row>
     <row r="28" spans="1:4" ht="29" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B29" t="s">
         <v>4</v>

--- a/ids541_specific/class_schedule_541_xlsx.xlsx
+++ b/ids541_specific/class_schedule_541_xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids541_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04336209-CB4E-B249-B640-5CEB49E5EC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51871800-9861-544B-83A4-551CE5989BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17520" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
   </bookViews>
@@ -99,9 +99,6 @@
 - `GIS Data Formats &lt;../notebooks/gis/60_gis_data.html&gt;`_</t>
   </si>
   <si>
-    <t>- `Link &lt;exercises/exercise_bigdata.html&gt;`_</t>
-  </si>
-  <si>
     <t>- GIS: Mixing Vector and Raster</t>
   </si>
   <si>
@@ -262,13 +259,7 @@
     <t>- MLK DAY NO CLASS</t>
   </si>
   <si>
-    <t>- `Mapping &lt;exercises/exercise_mapping.html&gt;`_</t>
-  </si>
-  <si>
     <t>- `Mapping &lt;../notebooks/gis/25_gis_mapping.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `Census &lt;exercises/exercise_census.html&gt;`_</t>
   </si>
   <si>
     <t>- Community Detection
@@ -276,12 +267,6 @@
   </si>
   <si>
     <t>- More Dask</t>
-  </si>
-  <si>
-    <t>- `Dask &lt;exercises/exercise_dask.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `Dask ARCOS &lt;exercises/exercise_dask_arcos.html&gt;`_</t>
   </si>
   <si>
     <t>**SNOW**</t>
@@ -294,6 +279,21 @@
   </si>
   <si>
     <t>**SNOW AGAIN**</t>
+  </si>
+  <si>
+    <t>- `Link &lt;../exercises/exercise_bigdata.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Dask &lt;../exercises/exercise_dask.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Dask ARCOS &lt;../exercises/exercise_dask_arcos.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Census &lt;../exercises/exercise_census.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Mapping &lt;../exercises/exercise_mapping.html&gt;`_</t>
   </si>
 </sst>
 </file>
@@ -710,24 +710,24 @@
     </row>
     <row r="2" spans="1:4" ht="204" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="204" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>9</v>
@@ -735,15 +735,15 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>3</v>
@@ -752,20 +752,20 @@
         <v>5</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>6</v>
@@ -774,62 +774,62 @@
         <v>7</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="118" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>76</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>17</v>
@@ -837,10 +837,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>16</v>
@@ -849,108 +849,108 @@
     </row>
     <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" s="8"/>
     </row>
     <row r="15" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" s="8"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="106" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>15</v>
@@ -961,7 +961,7 @@
     </row>
     <row r="24" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>15</v>
@@ -970,37 +970,37 @@
         <v>13</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="134" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="103" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
@@ -1012,18 +1012,18 @@
     </row>
     <row r="28" spans="1:4" ht="29" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B29" t="s">
         <v>4</v>

--- a/ids541_specific/class_schedule_541_xlsx.xlsx
+++ b/ids541_specific/class_schedule_541_xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids541_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51871800-9861-544B-83A4-551CE5989BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14192DB-CC6E-0C43-AF35-9127050BA399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17520" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="78">
   <si>
     <t>Topic</t>
   </si>
@@ -208,12 +208,6 @@
   </si>
   <si>
     <t>- `PGDA Chpt 7 through 7.2 (x-array) &lt;https://pythongis.org/part2/chapter-07/nb/0-learning-objectives.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `PGDA 7.3 through "Creating a raster mosaic by merging datasets" &lt;https://pythongis.org/part2/chapter-07/nb/02-common-raster-operations.html&gt;`_ (stop before Raster to vector conversion)</t>
-  </si>
-  <si>
-    <t>- `PGDA 7.5 &lt;https://pythongis.org/part2/chapter-07/nb/04-map-algebra.html&gt;`_</t>
   </si>
   <si>
     <t>- `PGDA 7.4 &lt;https://pythongis.org/part2/chapter-07/nb/03-coordinate-reference-systems-raster.html&gt;`_
@@ -243,9 +237,6 @@
 - Supervised ML Workflow</t>
   </si>
   <si>
-    <t>- `PGDA 7.3 "Raster to vector conversion" and "Vector to raster conversion" &lt;https://pythongis.org/part2/chapter-07/nb/02-common-raster-operations.html#raster-to-vector-conversion-vectorize&gt;`_</t>
-  </si>
-  <si>
     <t>- `Link &lt;../exercises/exercise_reshaping.html&gt;`_</t>
   </si>
   <si>
@@ -293,7 +284,19 @@
     <t>- `Census &lt;../exercises/exercise_census.html&gt;`_</t>
   </si>
   <si>
-    <t>- `Mapping &lt;../exercises/exercise_mapping.html&gt;`_</t>
+    <t>- `PGDA 7.3 through "Creating a raster mosaic by merging datasets" &lt;https://pythongis.org/part2/chapter-07/nb/02-common-raster-operations.html&gt;`_ (stop before Raster to vector conversion)
+- `PGDA 7.5 stop before Zonal Statistics with Vector Zones &lt;https://pythongis.org/part2/chapter-07/nb/04-map-algebra.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `PGDA 7.3 "Raster to vector conversion" and "Vector to raster conversion" &lt;https://pythongis.org/part2/chapter-07/nb/02-common-raster-operations.html#raster-to-vector-conversion-vectorize&gt;`_
+- `PGDA 7.5 Zonal Statistics with Vector Zones &lt;https://pythongis.org/part2/chapter-07/nb/04-map-algebra.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Projections &lt;../exercises/exercise_projections.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Mapping &lt;../exercises/exercise_mapping.html&gt;`_
+- Colormaps</t>
   </si>
 </sst>
 </file>
@@ -713,13 +716,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="204" customHeight="1" x14ac:dyDescent="0.2">
@@ -727,7 +730,7 @@
         <v>24</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>9</v>
@@ -738,7 +741,7 @@
         <v>25</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="60" x14ac:dyDescent="0.2">
@@ -752,7 +755,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -760,7 +763,7 @@
         <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.2">
@@ -774,7 +777,7 @@
         <v>7</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -782,7 +785,7 @@
         <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="118" customHeight="1" x14ac:dyDescent="0.2">
@@ -790,10 +793,10 @@
         <v>30</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="68" x14ac:dyDescent="0.2">
@@ -804,13 +807,13 @@
         <v>20</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -818,9 +821,9 @@
         <v>20</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>77</v>
       </c>
     </row>
@@ -834,6 +837,9 @@
       <c r="C12" s="9" t="s">
         <v>17</v>
       </c>
+      <c r="D12" s="11" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -859,7 +865,7 @@
       </c>
       <c r="D14" s="8"/>
     </row>
-    <row r="15" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -867,30 +873,30 @@
         <v>19</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>37</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="C16" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="45" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>38</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>56</v>
+        <v>18</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -915,18 +921,18 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="B20" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>42</v>
       </c>
@@ -934,7 +940,7 @@
         <v>15</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="106" customHeight="1" x14ac:dyDescent="0.2">
@@ -945,7 +951,7 @@
         <v>15</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="140" customHeight="1" x14ac:dyDescent="0.2">
@@ -970,7 +976,7 @@
         <v>13</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="134" customHeight="1" x14ac:dyDescent="0.2">
@@ -981,10 +987,10 @@
         <v>52</v>
       </c>
       <c r="C25" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="103" customHeight="1" x14ac:dyDescent="0.2">
@@ -995,7 +1001,7 @@
         <v>52</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -1018,7 +1024,7 @@
         <v>10</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">

--- a/ids541_specific/class_schedule_541_xlsx.xlsx
+++ b/ids541_specific/class_schedule_541_xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids541_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14192DB-CC6E-0C43-AF35-9127050BA399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B583AC0-FE20-0F42-A0EA-6DCCEE061A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17520" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
+    <workbookView xWindow="0" yWindow="700" windowWidth="30240" windowHeight="17520" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
   </bookViews>
   <sheets>
     <sheet name="class_schedule_541" sheetId="1" r:id="rId1"/>
@@ -91,9 +91,6 @@
     <t>- Machine Learning</t>
   </si>
   <si>
-    <t>- `Spatial Joins &lt;../notebooks/gis/30_gis_spatial_joins.html&gt;`_</t>
-  </si>
-  <si>
     <t>- `Projections &lt;../notebooks/gis/40_gis_projections.html&gt;`_
 - `Projections and Geopandas &lt;../notebooks/gis/50_gis_crs_geopandas.html&gt;`_
 - `GIS Data Formats &lt;../notebooks/gis/60_gis_data.html&gt;`_</t>
@@ -297,6 +294,11 @@
   <si>
     <t>- `Mapping &lt;../exercises/exercise_mapping.html&gt;`_
 - Colormaps</t>
+  </si>
+  <si>
+    <t>- `Spatial Joins &lt;../notebooks/gis/30_gis_spatial_joins.html&gt;`_
+- `Set Operations &lt;https://geopandas.org/en/stable/docs/user_guide/set_operations.html&gt;`_
+(Yes, this is just the docs. But I wrote a lot of them so it's not cheating!)</t>
   </si>
 </sst>
 </file>
@@ -713,24 +715,24 @@
     </row>
     <row r="2" spans="1:4" ht="204" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="204" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>9</v>
@@ -738,15 +740,15 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>3</v>
@@ -755,20 +757,20 @@
         <v>5</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>6</v>
@@ -777,186 +779,186 @@
         <v>7</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="118" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="43" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>34</v>
-      </c>
       <c r="B13" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" s="8"/>
     </row>
     <row r="15" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D15" s="8"/>
     </row>
     <row r="16" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="45" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="106" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>15</v>
@@ -967,7 +969,7 @@
     </row>
     <row r="24" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>15</v>
@@ -976,37 +978,37 @@
         <v>13</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="134" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="103" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
@@ -1018,18 +1020,18 @@
     </row>
     <row r="28" spans="1:4" ht="29" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B29" t="s">
         <v>4</v>

--- a/ids541_specific/class_schedule_541_xlsx.xlsx
+++ b/ids541_specific/class_schedule_541_xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids541_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B583AC0-FE20-0F42-A0EA-6DCCEE061A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C1DD4F-1000-D446-987E-2FC6D0B6CC54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="30240" windowHeight="17520" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
   </bookViews>

--- a/ids541_specific/class_schedule_541_xlsx.xlsx
+++ b/ids541_specific/class_schedule_541_xlsx.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C1DD4F-1000-D446-987E-2FC6D0B6CC54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="700" windowWidth="30240" windowHeight="17520" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
   </bookViews>
   <sheets>
     <sheet name="class_schedule_541" sheetId="1" r:id="rId1"/>

--- a/ids541_specific/class_schedule_541_xlsx.xlsx
+++ b/ids541_specific/class_schedule_541_xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids541_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C1DD4F-1000-D446-987E-2FC6D0B6CC54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A5B8905-4F57-6042-A180-594B3EE12792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17500" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
   </bookViews>
   <sheets>
     <sheet name="class_schedule_541" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="79">
   <si>
     <t>Topic</t>
   </si>
@@ -299,6 +299,9 @@
     <t>- `Spatial Joins &lt;../notebooks/gis/30_gis_spatial_joins.html&gt;`_
 - `Set Operations &lt;https://geopandas.org/en/stable/docs/user_guide/set_operations.html&gt;`_
 (Yes, this is just the docs. But I wrote a lot of them so it's not cheating!)</t>
+  </si>
+  <si>
+    <t>- `Joins &lt;../exercises/exercise_spatialjoins.html&gt;`_</t>
   </si>
 </sst>
 </file>
@@ -853,7 +856,9 @@
       <c r="C13" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D13" s="7"/>
+      <c r="D13" s="11" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">

--- a/ids541_specific/class_schedule_541_xlsx.xlsx
+++ b/ids541_specific/class_schedule_541_xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids541_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A5B8905-4F57-6042-A180-594B3EE12792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4CA18482-DC8B-8D44-B5BD-FE3E01ECF731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17500" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="79">
   <si>
     <t>Topic</t>
   </si>
@@ -250,10 +250,6 @@
     <t>- `Mapping &lt;../notebooks/gis/25_gis_mapping.html&gt;`_</t>
   </si>
   <si>
-    <t>- Community Detection
-- Shortest Path</t>
-  </si>
-  <si>
     <t>- More Dask</t>
   </si>
   <si>
@@ -302,6 +298,9 @@
   </si>
   <si>
     <t>- `Joins &lt;../exercises/exercise_spatialjoins.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- WORK DAY</t>
   </si>
 </sst>
 </file>
@@ -760,7 +759,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -768,7 +767,7 @@
         <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.2">
@@ -782,7 +781,7 @@
         <v>7</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -790,7 +789,7 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="118" customHeight="1" x14ac:dyDescent="0.2">
@@ -798,10 +797,10 @@
         <v>29</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="68" x14ac:dyDescent="0.2">
@@ -812,10 +811,10 @@
         <v>19</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -829,7 +828,7 @@
         <v>63</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="51" x14ac:dyDescent="0.2">
@@ -843,7 +842,7 @@
         <v>16</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="43" x14ac:dyDescent="0.2">
@@ -854,25 +853,22 @@
         <v>19</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="D13" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="D14" s="8"/>
     </row>
-    <row r="15" spans="1:4" ht="68" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -880,11 +876,11 @@
         <v>18</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -892,18 +888,18 @@
         <v>18</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>37</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>74</v>
+        <v>18</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -928,18 +924,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" ht="45" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -947,7 +943,7 @@
         <v>15</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="106" customHeight="1" x14ac:dyDescent="0.2">
@@ -969,7 +965,7 @@
         <v>15</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -980,25 +976,21 @@
         <v>15</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>56</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="D24" s="7"/>
     </row>
     <row r="25" spans="1:4" ht="134" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>45</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>57</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="D25" s="6"/>
     </row>
     <row r="26" spans="1:4" ht="103" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
@@ -1007,23 +999,28 @@
       <c r="B26" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C26" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="75" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>47</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="8"/>
-    </row>
-    <row r="28" spans="1:4" ht="29" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>48</v>
       </c>
@@ -1031,7 +1028,7 @@
         <v>10</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">

--- a/ids541_specific/class_schedule_541_xlsx.xlsx
+++ b/ids541_specific/class_schedule_541_xlsx.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids541_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4CA18482-DC8B-8D44-B5BD-FE3E01ECF731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B20EEB-5A78-4045-B68F-E217780156AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17500" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="77">
   <si>
     <t>Topic</t>
   </si>
@@ -96,9 +96,6 @@
 - `GIS Data Formats &lt;../notebooks/gis/60_gis_data.html&gt;`_</t>
   </si>
   <si>
-    <t>- GIS: Mixing Vector and Raster</t>
-  </si>
-  <si>
     <t>- GIS: Rasters</t>
   </si>
   <si>
@@ -205,10 +202,6 @@
   </si>
   <si>
     <t>- `PGDA Chpt 7 through 7.2 (x-array) &lt;https://pythongis.org/part2/chapter-07/nb/0-learning-objectives.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `PGDA 7.4 &lt;https://pythongis.org/part2/chapter-07/nb/03-coordinate-reference-systems-raster.html&gt;`_
-- `PGDA 7.3 Resampling Section &lt;https://pythongis.org/part2/chapter-07/nb/02-common-raster-operations.html#resampling-raster-data&gt;`_</t>
   </si>
   <si>
     <t>- Defensive Programming: from `first reading &lt;../notebooks/PDS_not_yet_in_coursera/20_programming_concepts/defensive_programming.html&gt;`_ through `Iceberg Principle &lt;../notebooks/PDS_not_yet_in_coursera/20_programming_concepts/iceberg_principle.html&gt;`_
@@ -277,14 +270,6 @@
     <t>- `Census &lt;../exercises/exercise_census.html&gt;`_</t>
   </si>
   <si>
-    <t>- `PGDA 7.3 through "Creating a raster mosaic by merging datasets" &lt;https://pythongis.org/part2/chapter-07/nb/02-common-raster-operations.html&gt;`_ (stop before Raster to vector conversion)
-- `PGDA 7.5 stop before Zonal Statistics with Vector Zones &lt;https://pythongis.org/part2/chapter-07/nb/04-map-algebra.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `PGDA 7.3 "Raster to vector conversion" and "Vector to raster conversion" &lt;https://pythongis.org/part2/chapter-07/nb/02-common-raster-operations.html#raster-to-vector-conversion-vectorize&gt;`_
-- `PGDA 7.5 Zonal Statistics with Vector Zones &lt;https://pythongis.org/part2/chapter-07/nb/04-map-algebra.html&gt;`_</t>
-  </si>
-  <si>
     <t>- `Projections &lt;../exercises/exercise_projections.html&gt;`_</t>
   </si>
   <si>
@@ -301,6 +286,15 @@
   </si>
   <si>
     <t>- WORK DAY</t>
+  </si>
+  <si>
+    <t>- `PGDA 7.3 through "Creating a raster mosaic by merging datasets" &lt;https://pythongis.org/part2/chapter-07/nb/02-common-raster-operations.html&gt;`_ (stop before Raster to vector conversion)
+- `PGDA 7.5 &lt;https://pythongis.org/part2/chapter-07/nb/04-map-algebra.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `PGDA 7.4 &lt;https://pythongis.org/part2/chapter-07/nb/03-coordinate-reference-systems-raster.html&gt;`_
+- `PGDA 7.3 Resampling Section &lt;https://pythongis.org/part2/chapter-07/nb/02-common-raster-operations.html#resampling-raster-data&gt;`_
+- `PGDA 7.3 "Raster to vector conversion" and "Vector to raster conversion" &lt;https://pythongis.org/part2/chapter-07/nb/02-common-raster-operations.html#raster-to-vector-conversion-vectorize&gt;`_</t>
   </si>
 </sst>
 </file>
@@ -717,24 +711,24 @@
     </row>
     <row r="2" spans="1:4" ht="204" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="204" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>9</v>
@@ -742,15 +736,15 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>3</v>
@@ -759,20 +753,20 @@
         <v>5</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>6</v>
@@ -781,259 +775,253 @@
         <v>7</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="118" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="43" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D14" s="8"/>
     </row>
     <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="8"/>
+    </row>
+    <row r="16" spans="1:4" ht="177" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="8"/>
-    </row>
-    <row r="16" spans="1:4" ht="68" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="B16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="85" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="51" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>37</v>
-      </c>
       <c r="B17" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>40</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="51" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>41</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="106" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D24" s="7"/>
     </row>
     <row r="25" spans="1:4" ht="134" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="D25" s="6"/>
     </row>
     <row r="26" spans="1:4" ht="103" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="9" t="s">
+      <c r="B27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="75" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>47</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B29" t="s">
         <v>4</v>

--- a/ids541_specific/class_schedule_541_xlsx.xlsx
+++ b/ids541_specific/class_schedule_541_xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids541_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B20EEB-5A78-4045-B68F-E217780156AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB90A82-ADBE-5647-8E0B-D31630F30A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17500" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
   </bookViews>
@@ -292,9 +292,9 @@
 - `PGDA 7.5 &lt;https://pythongis.org/part2/chapter-07/nb/04-map-algebra.html&gt;`_</t>
   </si>
   <si>
-    <t>- `PGDA 7.4 &lt;https://pythongis.org/part2/chapter-07/nb/03-coordinate-reference-systems-raster.html&gt;`_
-- `PGDA 7.3 Resampling Section &lt;https://pythongis.org/part2/chapter-07/nb/02-common-raster-operations.html#resampling-raster-data&gt;`_
-- `PGDA 7.3 "Raster to vector conversion" and "Vector to raster conversion" &lt;https://pythongis.org/part2/chapter-07/nb/02-common-raster-operations.html#raster-to-vector-conversion-vectorize&gt;`_</t>
+    <t>- `Finish PGDA 7.3 (Creating a raster mosaic sub section to the end) &lt;https://pythongis.org/part2/chapter-07/nb/02-common-raster-operations.html#creating-a-raster-mosaic-by-merging-datasets&gt;`_
+- `PGDA 7.4 &lt;https://pythongis.org/part2/chapter-07/nb/03-coordinate-reference-systems-raster.html&gt;`_
+- `Reproject Match &lt;https://corteva.github.io/rioxarray/stable/examples/reproject_match.html&gt;`_</t>
   </si>
 </sst>
 </file>
@@ -885,7 +885,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="85" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>36</v>
       </c>

--- a/ids541_specific/class_schedule_541_xlsx.xlsx
+++ b/ids541_specific/class_schedule_541_xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids541_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB90A82-ADBE-5647-8E0B-D31630F30A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30621FA7-F0BF-B04B-8D23-1F67A1D4C4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17500" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17500" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
   </bookViews>
   <sheets>
     <sheet name="class_schedule_541" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="78">
   <si>
     <t>Topic</t>
   </si>
@@ -295,6 +295,9 @@
     <t>- `Finish PGDA 7.3 (Creating a raster mosaic sub section to the end) &lt;https://pythongis.org/part2/chapter-07/nb/02-common-raster-operations.html#creating-a-raster-mosaic-by-merging-datasets&gt;`_
 - `PGDA 7.4 &lt;https://pythongis.org/part2/chapter-07/nb/03-coordinate-reference-systems-raster.html&gt;`_
 - `Reproject Match &lt;https://corteva.github.io/rioxarray/stable/examples/reproject_match.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Rasters &lt;../exercises/exercise_rasters.html&gt;`_</t>
   </si>
 </sst>
 </file>
@@ -884,6 +887,9 @@
       <c r="C16" s="9" t="s">
         <v>75</v>
       </c>
+      <c r="D16" s="11" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="17" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A17" t="s">

--- a/ids541_specific/class_schedule_541_xlsx.xlsx
+++ b/ids541_specific/class_schedule_541_xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids541_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30621FA7-F0BF-B04B-8D23-1F67A1D4C4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA0C3735-CCDC-E948-BF94-27A419B14B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17500" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17260" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
   </bookViews>
   <sheets>
     <sheet name="class_schedule_541" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="79">
   <si>
     <t>Topic</t>
   </si>
@@ -298,6 +298,9 @@
   </si>
   <si>
     <t>- `Rasters &lt;../exercises/exercise_rasters.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- Choose your own &lt;../exercises/exercise_choose_your_own_adventure.html&gt;`_</t>
   </si>
 </sst>
 </file>
@@ -901,6 +904,9 @@
       <c r="C17" s="9" t="s">
         <v>76</v>
       </c>
+      <c r="D17" s="11" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">

--- a/ids541_specific/class_schedule_541_xlsx.xlsx
+++ b/ids541_specific/class_schedule_541_xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids541_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA0C3735-CCDC-E948-BF94-27A419B14B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39713F7D-E988-3245-89E5-389DB7CA5193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17260" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
   </bookViews>
@@ -300,7 +300,7 @@
     <t>- `Rasters &lt;../exercises/exercise_rasters.html&gt;`_</t>
   </si>
   <si>
-    <t>- Choose your own &lt;../exercises/exercise_choose_your_own_adventure.html&gt;`_</t>
+    <t>- `Choose your own &lt;../exercises/exercise_choose_your_own_adventure.html&gt;`_</t>
   </si>
 </sst>
 </file>

--- a/ids541_specific/class_schedule_541_xlsx.xlsx
+++ b/ids541_specific/class_schedule_541_xlsx.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids541_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39713F7D-E988-3245-89E5-389DB7CA5193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB508ED-1889-4E45-BCAE-853DD047A4CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17260" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="82">
   <si>
     <t>Topic</t>
   </si>
@@ -301,6 +301,16 @@
   </si>
   <si>
     <t>- `Choose your own &lt;../exercises/exercise_choose_your_own_adventure.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- Data Science Questions</t>
+  </si>
+  <si>
+    <t>- `Solving Probs with Data &lt;https://ds4humans.com/10_introduction/10_solving_problems_with_data.html&gt;`_
+- `Solving Right Problem (include second page with  solving wrong problem example) &lt;https://ds4humans.com/20_problems_to_questions/10_solving_the_right_problem.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Answering Questions (include inference/prediction comparison) &lt;https://ds4humans.com/30_questions/00_solving_problems_by_answering_questions.html&gt;`_</t>
   </si>
 </sst>
 </file>
@@ -935,10 +945,10 @@
         <v>39</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="34" x14ac:dyDescent="0.2">
@@ -946,10 +956,10 @@
         <v>40</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="106" customHeight="1" x14ac:dyDescent="0.2">
@@ -960,7 +970,7 @@
         <v>15</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="140" customHeight="1" x14ac:dyDescent="0.2">
@@ -971,10 +981,10 @@
         <v>15</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>43</v>
       </c>
@@ -982,7 +992,7 @@
         <v>15</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="D24" s="7"/>
     </row>
@@ -994,7 +1004,7 @@
         <v>50</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="D25" s="6"/>
     </row>
@@ -1005,30 +1015,33 @@
       <c r="B26" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>52</v>
+      <c r="C26" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" ht="136" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>46</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>11</v>
+      <c r="C27" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" ht="75" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>47</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
@@ -1037,6 +1050,9 @@
       </c>
       <c r="B29" t="s">
         <v>4</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">

--- a/ids541_specific/class_schedule_541_xlsx.xlsx
+++ b/ids541_specific/class_schedule_541_xlsx.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids541_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB508ED-1889-4E45-BCAE-853DD047A4CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286C865F-8841-EB41-A5B7-444EAEEC9AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17260" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="83">
   <si>
     <t>Topic</t>
   </si>
@@ -311,6 +311,9 @@
   </si>
   <si>
     <t>- `Answering Questions (include inference/prediction comparison) &lt;https://ds4humans.com/30_questions/00_solving_problems_by_answering_questions.html&gt;`_</t>
+  </si>
+  <si>
+    <t>`Questions Ex &lt;https://ds4humans.com/99_exercises/exercise_probs_and_questions.html&gt;`_</t>
   </si>
 </sst>
 </file>
@@ -951,7 +954,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -960,6 +963,9 @@
       </c>
       <c r="C21" s="9" t="s">
         <v>81</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="106" customHeight="1" x14ac:dyDescent="0.2">

--- a/ids541_specific/class_schedule_541_xlsx.xlsx
+++ b/ids541_specific/class_schedule_541_xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids541_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286C865F-8841-EB41-A5B7-444EAEEC9AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{630AEF59-745A-244F-9111-7486898CEB33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17260" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="80">
   <si>
     <t>Topic</t>
   </si>
@@ -215,16 +215,6 @@
 - If you don't have a github account, make one. Register a passkey or at least two factor authentication.
 - `Add your ssh key to your github account &lt;https://docs.github.com/en/authentication/connecting-to-github-with-ssh/adding-a-new-ssh-key-to-your-github-account&gt;`_
 - `Visualize Git Branches &lt;https://learngitbranching.js.org/&gt;`_</t>
-  </si>
-  <si>
-    <t>- `Ex 1 &lt;../exercises/exercise_git.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `Ex 1 &lt;../exercises/exercise_git_2.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `Inference and Prediction &lt;../notebooks/class_5/week_3/20_inference_v_prediction.html&gt;`_
-- Supervised ML Workflow</t>
   </si>
   <si>
     <t>- `Link &lt;../exercises/exercise_reshaping.html&gt;`_</t>
@@ -733,13 +723,13 @@
         <v>21</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="204" customHeight="1" x14ac:dyDescent="0.2">
@@ -747,7 +737,7 @@
         <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>9</v>
@@ -758,7 +748,7 @@
         <v>23</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="60" x14ac:dyDescent="0.2">
@@ -772,7 +762,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -780,7 +770,7 @@
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.2">
@@ -794,7 +784,7 @@
         <v>7</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -802,7 +792,7 @@
         <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="118" customHeight="1" x14ac:dyDescent="0.2">
@@ -810,10 +800,10 @@
         <v>28</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="68" x14ac:dyDescent="0.2">
@@ -824,10 +814,10 @@
         <v>18</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -838,10 +828,10 @@
         <v>18</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="51" x14ac:dyDescent="0.2">
@@ -855,7 +845,7 @@
         <v>16</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="43" x14ac:dyDescent="0.2">
@@ -866,10 +856,10 @@
         <v>18</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -877,7 +867,7 @@
         <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D14" s="8"/>
     </row>
@@ -901,10 +891,10 @@
         <v>17</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="68" x14ac:dyDescent="0.2">
@@ -915,10 +905,10 @@
         <v>17</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -948,10 +938,10 @@
         <v>39</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="51" x14ac:dyDescent="0.2">
@@ -959,13 +949,13 @@
         <v>40</v>
       </c>
       <c r="B21" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>79</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="106" customHeight="1" x14ac:dyDescent="0.2">
@@ -987,10 +977,10 @@
         <v>15</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>43</v>
       </c>
@@ -998,7 +988,7 @@
         <v>15</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="D24" s="7"/>
     </row>
@@ -1010,7 +1000,7 @@
         <v>50</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="D25" s="6"/>
     </row>
@@ -1021,33 +1011,26 @@
       <c r="B26" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="136" x14ac:dyDescent="0.2">
+      <c r="C26" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" s="6"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>46</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="75" x14ac:dyDescent="0.2">
+      <c r="C27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="6"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>47</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
@@ -1056,9 +1039,6 @@
       </c>
       <c r="B29" t="s">
         <v>4</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">

--- a/ids541_specific/class_schedule_541_xlsx.xlsx
+++ b/ids541_specific/class_schedule_541_xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids541_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{630AEF59-745A-244F-9111-7486898CEB33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96654E80-BC6F-2443-AB2A-90DB6273299A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17260" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="81">
   <si>
     <t>Topic</t>
   </si>
@@ -83,9 +83,6 @@
   </si>
   <si>
     <t>- SciKit-Learn</t>
-  </si>
-  <si>
-    <t>- Supervised ML</t>
   </si>
   <si>
     <t>- Machine Learning</t>
@@ -304,6 +301,13 @@
   </si>
   <si>
     <t>`Questions Ex &lt;https://ds4humans.com/99_exercises/exercise_probs_and_questions.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Pandas, Numpy, and Patsy &lt;https://www.practicaldatascience.org/notebooks/class_5/week_3/35_pandas_to_numpy_with_patsy.html&gt;`_
+- Spend more time with Géron 1 and 2</t>
+  </si>
+  <si>
+    <t>`Supervised ML &lt;https://ds4humans.com/99_exercises/exercise_passiveprediction_workflow.html&gt;`_</t>
   </si>
 </sst>
 </file>
@@ -720,24 +724,24 @@
     </row>
     <row r="2" spans="1:4" ht="204" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="204" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>9</v>
@@ -745,15 +749,15 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>3</v>
@@ -762,20 +766,20 @@
         <v>5</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>6</v>
@@ -784,208 +788,211 @@
         <v>7</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="118" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="43" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>69</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D14" s="8"/>
     </row>
     <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" s="8"/>
     </row>
     <row r="16" spans="1:4" ht="177" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>76</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C21" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>78</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="106" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>13</v>
@@ -994,31 +1001,31 @@
     </row>
     <row r="25" spans="1:4" ht="134" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D25" s="6"/>
     </row>
     <row r="26" spans="1:4" ht="103" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D26" s="6"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
@@ -1030,12 +1037,12 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B29" t="s">
         <v>4</v>

--- a/ids541_specific/class_schedule_541_xlsx.xlsx
+++ b/ids541_specific/class_schedule_541_xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids541_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96654E80-BC6F-2443-AB2A-90DB6273299A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D014C0CA-3AC7-FE48-8809-A5A5EDFB40E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17260" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="82">
   <si>
     <t>Topic</t>
   </si>
@@ -80,9 +80,6 @@
   </si>
   <si>
     <t>**NO CLASS**</t>
-  </si>
-  <si>
-    <t>- SciKit-Learn</t>
   </si>
   <si>
     <t>- Machine Learning</t>
@@ -308,6 +305,14 @@
   </si>
   <si>
     <t>`Supervised ML &lt;https://ds4humans.com/99_exercises/exercise_passiveprediction_workflow.html&gt;`_</t>
+  </si>
+  <si>
+    <t>`Passive P Ex &lt;https://ds4humans.com/99_exercises/exercise_passive_prediction.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Chpt 9 &lt;https://ds4humans.com/30_questions/20_using_passive_prediction_questions.html&gt;`_
+- `Chpt 10 &lt;https://ds4humans.com/30_questions/23_passive_internal_alignment_and_bias.html&gt;`_
+- `Chpt 11 &lt;https://ds4humans.com/30_questions/24_passive_internal_errors.html&gt;`_ ONLY FIRST READING, not Fairness</t>
   </si>
 </sst>
 </file>
@@ -724,24 +729,24 @@
     </row>
     <row r="2" spans="1:4" ht="204" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="204" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>9</v>
@@ -749,15 +754,15 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>3</v>
@@ -766,20 +771,20 @@
         <v>5</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>6</v>
@@ -788,244 +793,246 @@
         <v>7</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="118" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="43" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>68</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" s="8"/>
     </row>
     <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" s="8"/>
     </row>
     <row r="16" spans="1:4" ht="177" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>75</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C21" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>77</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="106" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>80</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>42</v>
-      </c>
       <c r="B24" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="7"/>
+        <v>81</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="25" spans="1:4" ht="134" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D25" s="6"/>
     </row>
     <row r="26" spans="1:4" ht="103" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D26" s="6"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
@@ -1037,12 +1044,18 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>46</v>
+        <v>45</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B29" t="s">
         <v>4</v>

--- a/ids541_specific/class_schedule_541_xlsx.xlsx
+++ b/ids541_specific/class_schedule_541_xlsx.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids541_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D014C0CA-3AC7-FE48-8809-A5A5EDFB40E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75E87EB-925D-7B44-B37D-DB0540AC8AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17260" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="84">
   <si>
     <t>Topic</t>
   </si>
@@ -313,6 +313,12 @@
     <t>- `Chpt 9 &lt;https://ds4humans.com/30_questions/20_using_passive_prediction_questions.html&gt;`_
 - `Chpt 10 &lt;https://ds4humans.com/30_questions/23_passive_internal_alignment_and_bias.html&gt;`_
 - `Chpt 11 &lt;https://ds4humans.com/30_questions/24_passive_internal_errors.html&gt;`_ ONLY FIRST READING, not Fairness</t>
+  </si>
+  <si>
+    <t>- `Git 1 &lt;../exercises/exercise_git.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Git 2 &lt;../exercises/exercise_git_2.html&gt;`_</t>
   </si>
 </sst>
 </file>
@@ -1016,7 +1022,9 @@
       <c r="C25" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="6"/>
+      <c r="D25" s="7" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="26" spans="1:4" ht="103" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
@@ -1028,7 +1036,9 @@
       <c r="C26" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="6"/>
+      <c r="D26" s="7" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">

--- a/ids541_specific/class_schedule_541_xlsx.xlsx
+++ b/ids541_specific/class_schedule_541_xlsx.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids541_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75E87EB-925D-7B44-B37D-DB0540AC8AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF19B322-392D-A544-8E3D-41B1CFB7E691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17260" xr2:uid="{212B26BE-C12B-1745-A277-D3917F547107}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="85">
   <si>
     <t>Topic</t>
   </si>
@@ -319,6 +319,9 @@
   </si>
   <si>
     <t>- `Git 2 &lt;../exercises/exercise_git_2.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Network Analysis, Chpt 1 and 2 &lt;https://ericmjl.github.io/Network-Analysis-Made-Simple/01-introduction/01-graphs/&gt;`_</t>
   </si>
 </sst>
 </file>
@@ -1048,7 +1051,7 @@
         <v>10</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="D27" s="6"/>
     </row>
